--- a/data/trans_orig/Q5406-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5406-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de tomar medicación en 2007</t>
+          <t>Población según si es capaz de tomar medicación en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>6624</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7152</t>
+          <t>7538</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24119</t>
+          <t>24001</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9157</t>
+          <t>8880</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26072</t>
+          <t>25812</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18016</t>
+          <t>17375</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37104</t>
+          <t>35812</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16389</t>
+          <t>16745</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37106</t>
+          <t>36980</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38693</t>
+          <t>39114</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66716</t>
+          <t>66035</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>334208</t>
+          <t>335692</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>354009</t>
+          <t>354576</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>535411</t>
+          <t>532124</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>560407</t>
+          <t>558914</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>876380</t>
+          <t>876351</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>908287</t>
+          <t>908203</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,51%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8504</t>
+          <t>10543</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>7270</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>914</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11024</t>
+          <t>11519</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>799</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7016</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5672</t>
+          <t>5661</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>943</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9419</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77451</t>
+          <t>76766</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86487</t>
+          <t>87115</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53598</t>
+          <t>53434</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61303</t>
+          <t>61287</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>135884</t>
+          <t>133896</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>147417</t>
+          <t>146879</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -1645,97 +1645,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>2068</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1758,97 +1758,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2068</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39010</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41194</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25052</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26881</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66007</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68075</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>978</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11315</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>8806</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26077</t>
+          <t>26103</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12085</t>
+          <t>11451</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30871</t>
+          <t>31081</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19459</t>
+          <t>20165</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39581</t>
+          <t>39029</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17944</t>
+          <t>18306</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39628</t>
+          <t>39804</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42220</t>
+          <t>41733</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69796</t>
+          <t>70483</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>458808</t>
+          <t>458908</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>479484</t>
+          <t>479717</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>618481</t>
+          <t>619463</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>645241</t>
+          <t>645182</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1087766</t>
+          <t>1086078</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1119455</t>
+          <t>1120894</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,05%</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de tomar medicación en 2012</t>
+          <t>Población según si es capaz de tomar medicación en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8556</t>
+          <t>9252</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24654</t>
+          <t>27055</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18489</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40670</t>
+          <t>41568</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32026</t>
+          <t>32934</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58113</t>
+          <t>59835</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21099</t>
+          <t>22109</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45532</t>
+          <t>44816</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34824</t>
+          <t>34917</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62664</t>
+          <t>62113</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>61552</t>
+          <t>61028</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>97645</t>
+          <t>96502</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>350522</t>
+          <t>352189</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>379219</t>
+          <t>379654</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>540640</t>
+          <t>540227</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>573986</t>
+          <t>573696</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>901633</t>
+          <t>905909</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>948474</t>
+          <t>946388</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,22%</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>5119</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>8026</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>992</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9063</t>
+          <t>8661</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13879</t>
+          <t>15893</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5532</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15168</t>
+          <t>15307</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>103908</t>
+          <t>102304</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>116509</t>
+          <t>116594</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72784</t>
+          <t>72861</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81983</t>
+          <t>82002</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>182965</t>
+          <t>182149</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>197471</t>
+          <t>197081</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -3700,97 +3700,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2296</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2222</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>9,99%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>2331</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3813,97 +3813,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2296</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5753</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>4,94%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>25,86%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1100</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5031</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,94%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>5529</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>22,61%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4900</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24279</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26575</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17215</t>
+          <t>16493</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>74,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>43921</t>
+          <t>43292</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9473</t>
+          <t>9567</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27148</t>
+          <t>26749</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21196</t>
+          <t>20803</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44071</t>
+          <t>43828</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35189</t>
+          <t>34229</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63818</t>
+          <t>63477</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25497</t>
+          <t>25123</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53498</t>
+          <t>51851</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36847</t>
+          <t>36529</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>64526</t>
+          <t>63712</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>68818</t>
+          <t>68990</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>106789</t>
+          <t>107174</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>485441</t>
+          <t>488591</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>518208</t>
+          <t>520073</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>639806</t>
+          <t>641545</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>675708</t>
+          <t>676252</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1144591</t>
+          <t>1139910</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1188876</t>
+          <t>1189191</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,51%</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de tomar medicación en 2016</t>
+          <t>Población según si es capaz de tomar medicación en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10848</t>
+          <t>12138</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21923</t>
+          <t>21214</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10314</t>
+          <t>10053</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28137</t>
+          <t>27816</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11979</t>
+          <t>11286</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28299</t>
+          <t>27282</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23072</t>
+          <t>23480</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48426</t>
+          <t>49617</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39241</t>
+          <t>39762</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69268</t>
+          <t>70471</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>319695</t>
+          <t>319924</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>337360</t>
+          <t>338176</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>491825</t>
+          <t>492010</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>521441</t>
+          <t>521861</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>818614</t>
+          <t>819511</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>853900</t>
+          <t>853336</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,91%</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4228</t>
+          <t>4232</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10147</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11055</t>
+          <t>13397</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14109</t>
+          <t>13581</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14432</t>
+          <t>13382</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>188304</t>
+          <t>188300</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>171848</t>
+          <t>171193</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>185996</t>
+          <t>185949</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>362426</t>
+          <t>362097</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>377738</t>
+          <t>377759</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -5755,97 +5755,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1912</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2376</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>2132</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5868,97 +5868,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1376</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1912</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6446</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>4,09%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>19,14%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1376</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6650</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>6964</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>19,75%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1376</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>6917</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>40117</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42029</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27024</t>
+          <t>27228</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>68786</t>
+          <t>68739</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>3161</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12967</t>
+          <t>13040</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6332</t>
+          <t>6539</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24710</t>
+          <t>24307</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12554</t>
+          <t>12471</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33083</t>
+          <t>31712</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11725</t>
+          <t>11339</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26104</t>
+          <t>27114</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>27558</t>
+          <t>28686</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57454</t>
+          <t>57153</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>44145</t>
+          <t>44489</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>76899</t>
+          <t>77819</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>554388</t>
+          <t>554526</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>571828</t>
+          <t>571681</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>701963</t>
+          <t>702218</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>737359</t>
+          <t>735220</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1264103</t>
+          <t>1266305</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1302039</t>
+          <t>1303058</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,46%</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de tomar medicación en 2023</t>
+          <t>Población según si es capaz de tomar medicación en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2818</t>
+          <t>2953</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10181</t>
+          <t>11021</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16886</t>
+          <t>16122</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31324</t>
+          <t>31451</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21625</t>
+          <t>21237</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38528</t>
+          <t>37970</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11424</t>
+          <t>11324</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23657</t>
+          <t>23162</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33414</t>
+          <t>33275</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51119</t>
+          <t>50559</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47041</t>
+          <t>47766</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68615</t>
+          <t>69104</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>239231</t>
+          <t>239274</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>252671</t>
+          <t>252728</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>423697</t>
+          <t>424056</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>445220</t>
+          <t>445663</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>668037</t>
+          <t>668453</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>694131</t>
+          <t>694424</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,3%</t>
         </is>
       </c>
     </row>
@@ -7359,7 +7359,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t>3585</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4943</t>
+          <t>4684</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>595</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5407</t>
+          <t>5539</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8845</t>
+          <t>8720</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>2314</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20717</t>
+          <t>21198</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>6090</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>22818</t>
+          <t>22657</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>262866</t>
+          <t>262860</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>270541</t>
+          <t>270668</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>431701</t>
+          <t>431102</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>452022</t>
+          <t>452269</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>702413</t>
+          <t>702671</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>720741</t>
+          <t>720752</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,7 +7665,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -7810,97 +7810,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1192</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>1054</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>162</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5978</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3459</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>875</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6312</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99008</t>
+          <t>99655</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>104820</t>
+          <t>104824</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67866</t>
+          <t>67924</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>169999</t>
+          <t>170074</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>175487</t>
+          <t>175436</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11300</t>
+          <t>11421</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11248</t>
+          <t>13179</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34950</t>
+          <t>35753</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20330</t>
+          <t>20763</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41740</t>
+          <t>41369</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15732</t>
+          <t>16066</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30772</t>
+          <t>31014</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26544</t>
+          <t>28319</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>70155</t>
+          <t>70756</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47541</t>
+          <t>47443</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>91100</t>
+          <t>91877</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8469,7 +8469,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>609453</t>
+          <t>608789</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>626015</t>
+          <t>625224</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>925013</t>
+          <t>924874</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>989038</t>
+          <t>984293</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1545637</t>
+          <t>1545736</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1606702</t>
+          <t>1602728</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5406-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5406-Estudios-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>6281</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7538</t>
+          <t>6919</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24001</t>
+          <t>23948</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8880</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25812</t>
+          <t>25375</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17375</t>
+          <t>17478</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35812</t>
+          <t>35860</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16745</t>
+          <t>16769</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36980</t>
+          <t>37654</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39114</t>
+          <t>39373</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66035</t>
+          <t>65858</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>335692</t>
+          <t>335304</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>354576</t>
+          <t>354321</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>532124</t>
+          <t>533199</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>558914</t>
+          <t>559393</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>876351</t>
+          <t>875919</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>908203</t>
+          <t>907535</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,44%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10543</t>
+          <t>8388</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7270</t>
+          <t>6953</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>930</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11519</t>
+          <t>10742</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>829</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7022</t>
+          <t>7127</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5661</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>10877</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76766</t>
+          <t>76916</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87115</t>
+          <t>86419</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53434</t>
+          <t>53743</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61287</t>
+          <t>61307</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>133896</t>
+          <t>134605</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>146879</t>
+          <t>147034</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>854</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10575</t>
+          <t>10348</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8806</t>
+          <t>8915</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26103</t>
+          <t>25339</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11451</t>
+          <t>12169</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31081</t>
+          <t>32140</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20165</t>
+          <t>20458</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39029</t>
+          <t>39847</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18306</t>
+          <t>18609</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39804</t>
+          <t>39299</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41733</t>
+          <t>42359</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>70483</t>
+          <t>70845</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>458908</t>
+          <t>457728</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>479717</t>
+          <t>479103</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>619463</t>
+          <t>617242</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>645182</t>
+          <t>645162</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1086078</t>
+          <t>1087961</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1120894</t>
+          <t>1119725</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,95%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>9305</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27055</t>
+          <t>25472</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19166</t>
+          <t>19931</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41568</t>
+          <t>43746</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32934</t>
+          <t>33652</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59835</t>
+          <t>62754</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22109</t>
+          <t>21556</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44816</t>
+          <t>44934</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34917</t>
+          <t>34402</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62113</t>
+          <t>63417</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>61028</t>
+          <t>61437</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>96502</t>
+          <t>98034</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>352189</t>
+          <t>353684</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>379654</t>
+          <t>379891</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>540227</t>
+          <t>541003</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>573696</t>
+          <t>574898</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>905909</t>
+          <t>901769</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>946388</t>
+          <t>946961</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,28%</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5119</t>
+          <t>6044</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>999</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8661</t>
+          <t>9513</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15893</t>
+          <t>14447</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>6651</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15307</t>
+          <t>15321</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>102304</t>
+          <t>103424</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>116594</t>
+          <t>116587</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72861</t>
+          <t>73028</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82002</t>
+          <t>81991</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>182149</t>
+          <t>181931</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>197081</t>
+          <t>197255</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>5786</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16493</t>
+          <t>15417</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>43292</t>
+          <t>43035</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>9982</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26749</t>
+          <t>28577</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20803</t>
+          <t>21448</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43828</t>
+          <t>44738</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34229</t>
+          <t>35614</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63477</t>
+          <t>63153</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25123</t>
+          <t>25458</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51851</t>
+          <t>53171</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>36529</t>
+          <t>36708</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63712</t>
+          <t>64726</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>68990</t>
+          <t>68906</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>107174</t>
+          <t>106453</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>488591</t>
+          <t>487365</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>520073</t>
+          <t>519776</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>641545</t>
+          <t>640497</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>676252</t>
+          <t>675624</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1139910</t>
+          <t>1139884</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1189191</t>
+          <t>1188110</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,43%</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>2430</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12138</t>
+          <t>12057</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>6047</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21214</t>
+          <t>22336</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10053</t>
+          <t>9874</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27816</t>
+          <t>27872</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11286</t>
+          <t>11607</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27282</t>
+          <t>27095</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23480</t>
+          <t>23475</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49617</t>
+          <t>49592</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39762</t>
+          <t>38833</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>70471</t>
+          <t>70737</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>319924</t>
+          <t>319424</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>338176</t>
+          <t>337618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>492010</t>
+          <t>490681</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>521861</t>
+          <t>521082</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>819511</t>
+          <t>820405</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>853336</t>
+          <t>855143</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,11%</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>5087</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10177</t>
+          <t>9184</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13397</t>
+          <t>11997</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13581</t>
+          <t>14215</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13382</t>
+          <t>12655</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>188300</t>
+          <t>187445</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>171193</t>
+          <t>170632</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>185949</t>
+          <t>185956</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>362097</t>
+          <t>363772</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>377759</t>
+          <t>378484</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -5908,7 +5908,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6865</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>8506</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27228</t>
+          <t>26809</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,86%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>68739</t>
+          <t>67197</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3161</t>
+          <t>3204</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13040</t>
+          <t>12439</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6539</t>
+          <t>7261</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24307</t>
+          <t>24188</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12471</t>
+          <t>11562</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31712</t>
+          <t>32405</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11339</t>
+          <t>11454</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27114</t>
+          <t>27632</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28686</t>
+          <t>28504</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57153</t>
+          <t>56622</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>44489</t>
+          <t>43946</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>77819</t>
+          <t>76391</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>554526</t>
+          <t>553645</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>571681</t>
+          <t>571612</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>702218</t>
+          <t>702948</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>735220</t>
+          <t>735656</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1266305</t>
+          <t>1266023</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1303058</t>
+          <t>1303367</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -6893,32 +6893,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>5840</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2953</t>
+          <t>2842</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11021</t>
+          <t>10537</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6928,32 +6928,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>23073</t>
+          <t>24744</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16122</t>
+          <t>18058</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31451</t>
+          <t>33147</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>28871</t>
+          <t>30584</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21237</t>
+          <t>22748</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37970</t>
+          <t>40564</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -7006,32 +7006,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16473</t>
+          <t>17326</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11324</t>
+          <t>11477</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23162</t>
+          <t>24964</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7041,32 +7041,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>41332</t>
+          <t>43247</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33275</t>
+          <t>34737</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50559</t>
+          <t>53390</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>57806</t>
+          <t>60573</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47766</t>
+          <t>50056</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69104</t>
+          <t>72127</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -7119,32 +7119,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>246973</t>
+          <t>266928</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>239274</t>
+          <t>258757</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>252728</t>
+          <t>273624</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>435384</t>
+          <t>469766</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>424056</t>
+          <t>458318</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>445663</t>
+          <t>480533</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>682357</t>
+          <t>736696</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>668453</t>
+          <t>722356</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>694424</t>
+          <t>750037</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,6%</t>
         </is>
       </c>
     </row>
@@ -7232,17 +7232,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>269244</t>
+          <t>290095</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>269244</t>
+          <t>290095</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>269244</t>
+          <t>290095</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7267,17 +7267,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>499789</t>
+          <t>537757</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>499789</t>
+          <t>537757</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>499789</t>
+          <t>537757</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>769033</t>
+          <t>827853</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>769033</t>
+          <t>827853</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>769033</t>
+          <t>827853</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>610</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -7359,12 +7359,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3585</t>
+          <t>3195</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7384,32 +7384,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>460</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4684</t>
+          <t>3913</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>855</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5539</t>
+          <t>6074</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -7462,32 +7462,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4124</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8720</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7497,32 +7497,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9958</t>
+          <t>11109</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2314</t>
+          <t>7422</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21198</t>
+          <t>17186</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>14082</t>
+          <t>15302</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6090</t>
+          <t>10251</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>22657</t>
+          <t>22312</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -7575,32 +7575,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>267881</t>
+          <t>298354</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>262860</t>
+          <t>293650</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>270668</t>
+          <t>301199</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7610,32 +7610,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>443679</t>
+          <t>264336</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>431102</t>
+          <t>257760</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>452269</t>
+          <t>268396</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>711560</t>
+          <t>562690</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>702671</t>
+          <t>555245</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>720752</t>
+          <t>567977</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>97,87%</t>
         </is>
       </c>
     </row>
@@ -7688,17 +7688,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>272637</t>
+          <t>303157</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>272637</t>
+          <t>303157</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>272637</t>
+          <t>303157</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7723,17 +7723,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>455286</t>
+          <t>277178</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>455286</t>
+          <t>277178</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>455286</t>
+          <t>277178</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>727923</t>
+          <t>580335</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>727923</t>
+          <t>580335</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>727923</t>
+          <t>580335</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7918,32 +7918,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>165</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>6017</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -7963,12 +7963,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2629</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6237</t>
+          <t>7190</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -8031,32 +8031,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>103338</t>
+          <t>116695</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99655</t>
+          <t>112864</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>104824</t>
+          <t>118716</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8066,27 +8066,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>70344</t>
+          <t>81805</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67924</t>
+          <t>79456</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>173682</t>
+          <t>198501</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>170074</t>
+          <t>194546</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>175436</t>
+          <t>200674</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -8144,17 +8144,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8179,17 +8179,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8261,32 +8261,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11421</t>
+          <t>11361</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8296,32 +8296,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>24721</t>
+          <t>26477</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13179</t>
+          <t>19963</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35753</t>
+          <t>35553</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>31152</t>
+          <t>32927</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20763</t>
+          <t>25094</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41369</t>
+          <t>41640</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -8374,32 +8374,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>22245</t>
+          <t>23705</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16066</t>
+          <t>16629</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31014</t>
+          <t>32905</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8409,32 +8409,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>52272</t>
+          <t>55406</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28319</t>
+          <t>46169</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>70756</t>
+          <t>67468</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>74516</t>
+          <t>79111</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47443</t>
+          <t>66017</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>91877</t>
+          <t>92352</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -8487,32 +8487,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>618191</t>
+          <t>681979</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>608789</t>
+          <t>671635</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>625224</t>
+          <t>689444</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8522,32 +8522,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>949407</t>
+          <t>815908</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>924874</t>
+          <t>802218</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>984293</t>
+          <t>828268</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1567598</t>
+          <t>1497887</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1545736</t>
+          <t>1482803</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1602728</t>
+          <t>1513840</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>94,03%</t>
         </is>
       </c>
     </row>
@@ -8600,17 +8600,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>646866</t>
+          <t>712134</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>646866</t>
+          <t>712134</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>646866</t>
+          <t>712134</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8635,17 +8635,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1026400</t>
+          <t>897790</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1026400</t>
+          <t>897790</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1026400</t>
+          <t>897790</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1673266</t>
+          <t>1609924</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1673266</t>
+          <t>1609924</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1673266</t>
+          <t>1609924</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
